--- a/lcoe/ethylene/bio_ethylene_lcoe/LCOE_BIO_ETHYLENE_6.xlsx
+++ b/lcoe/ethylene/bio_ethylene_lcoe/LCOE_BIO_ETHYLENE_6.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abbie/Desktop/Dolphyn_to_Macro/Dolphyn vs. Macro/Python Codes/lcoe/ethylene/bio_ethylene_lcoe/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49BEF9DE-7E69-C546-8A54-D7920BCFE9FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53F53F7B-9654-9D42-9539-8D831623D8EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
